--- a/data/trans_camb/IP16B10-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B10-Habitat-trans_camb.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-75,07; 0,0</t>
+          <t>-73,45; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,07; 0,0</t>
+          <t>-73,45; 0,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-66,74; 0,0</t>
+          <t>-60,84; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-37,2; 0,0</t>
+          <t>-37,68; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 0,0</t>
+          <t>-65,77; 0,0</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-66,74; 0,0</t>
+          <t>-60,84; 0,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,2; 0,0</t>
+          <t>-37,68; 0,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,19; 0,0</t>
+          <t>-65,77; 0,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B10-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP16B10-Habitat-trans_camb.xlsx
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 0,0</t>
+          <t>-62,93; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 0,0</t>
+          <t>-40,62; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 0,0</t>
+          <t>-65,3; 0,0</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 0,0</t>
+          <t>-62,93; 0,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 0,0</t>
+          <t>-40,62; 0,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 0,0</t>
+          <t>-65,3; 0,0</t>
         </is>
       </c>
     </row>
